--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_jonesOutcomeMeasuresRodent2025.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_jonesOutcomeMeasuresRodent2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F872ECD-886F-C04B-B4EE-5D34ABA59D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263C652C-BD52-0940-8FEB-C866C8818E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35980" yWindow="3260" windowWidth="27640" windowHeight="16940" xr2:uid="{62FB4FD4-FC43-EC49-8283-9104746D43ED}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="9720" xr2:uid="{62FB4FD4-FC43-EC49-8283-9104746D43ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
   <si>
     <t>Test Name</t>
   </si>
@@ -251,10 +251,13 @@
     <t>Behavioral</t>
   </si>
   <si>
-    <t>Imaging &amp; Morphology</t>
-  </si>
-  <si>
     <t>Subdomain</t>
+  </si>
+  <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>Imaging</t>
   </si>
 </sst>
 </file>
@@ -662,7 +665,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -701,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -715,7 +718,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -729,7 +732,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -743,7 +746,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
